--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -734,14 +734,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -758,13 +757,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -800,12 +800,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">30226
 </t>
         </is>
       </c>
@@ -817,7 +818,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -829,13 +830,14 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -852,7 +854,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -877,7 +879,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -889,7 +891,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -901,7 +903,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -919,7 +921,8 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -936,8 +939,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -948,19 +950,19 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -978,19 +980,18 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>616</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -1007,8 +1008,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4316
 </t>
         </is>
       </c>
@@ -1056,13 +1056,13 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1072,10 +1072,16 @@
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">606
+</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1086,7 +1092,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1104,7 +1110,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1134,7 +1140,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1158,12 +1164,12 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1194,12 +1200,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1211,8 +1217,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1229,31 +1234,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1502
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">173
 </t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1173
-</t>
-        </is>
-      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1265,7 +1270,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3189
 </t>
         </is>
       </c>
@@ -1283,7 +1288,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1295,30 +1300,30 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -1337,26 +1342,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1367,13 +1368,13 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1384,8 +1385,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18656
 </t>
         </is>
       </c>
@@ -1408,13 +1408,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1456,25 +1456,25 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1492,42 +1492,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1538,19 +1533,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1568,7 +1561,8 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1584,7 +1578,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1607,18 +1602,19 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1643,8 +1639,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1655,7 +1650,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1666,14 +1661,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1684,11 +1677,15 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5447
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1697,13 +1694,13 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1721,8 +1718,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1733,31 +1729,29 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1769,7 +1763,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">8065
 </t>
         </is>
       </c>
@@ -1794,19 +1788,18 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450
+          <t xml:space="preserve">4456
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -1818,7 +1811,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -1830,13 +1823,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1857,7 +1850,12 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">879
@@ -1878,7 +1876,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1890,7 +1888,8 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1913,13 +1912,13 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -1956,8 +1955,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1968,8 +1966,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2010,7 +2007,8 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2021,19 +2019,19 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -2051,19 +2049,17 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -2081,7 +2077,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -2100,8 +2096,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
-</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2130,7 +2125,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2148,7 +2143,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -2166,14 +2161,13 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2184,7 +2178,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">4286
 </t>
         </is>
       </c>
@@ -2196,7 +2190,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">3247
 </t>
         </is>
       </c>
@@ -2214,14 +2208,13 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2232,8 +2225,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2257,7 +2249,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
@@ -2269,7 +2261,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2281,13 +2273,13 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2305,25 +2297,25 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2347,13 +2339,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2389,7 +2381,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2419,20 +2411,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2461,25 +2450,24 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2527,7 +2515,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2539,19 +2527,18 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2570,19 +2557,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -2624,26 +2611,31 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1609
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9186
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211222
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2654,12 +2646,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t xml:space="preserve">425
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2670,8 +2664,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2682,23 +2675,24 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>464</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2717,7 +2711,9 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t xml:space="preserve">1
+3986
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2734,32 +2730,28 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -2777,7 +2769,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2801,50 +2793,57 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2428
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2860,35 +2859,36 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373
+          <t xml:space="preserve">432
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2899,13 +2899,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2929,13 +2928,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2429
 </t>
         </is>
       </c>
@@ -2947,7 +2946,8 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2958,12 +2958,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>044</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2986,13 +2987,14 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">46
+8 179
 </t>
         </is>
       </c>
@@ -3035,20 +3037,19 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3059,8 +3060,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3071,13 +3071,13 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3125,8 +3125,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3137,18 +3136,21 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">212
+44
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">62
+818
 </t>
         </is>
       </c>
@@ -3167,40 +3169,42 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">3
+1 8 4
+7
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3212,13 +3216,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -3236,20 +3239,17 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3266,14 +3266,12 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3284,20 +3282,18 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="Z20" s="3" t="n"/>
@@ -3322,8 +3318,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3338,14 +3333,10 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3363,7 +3354,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3375,7 +3366,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3404,19 +3396,19 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">5310
 </t>
         </is>
       </c>
@@ -3428,23 +3420,25 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t xml:space="preserve">259
+8111
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3468,25 +3462,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3497,7 +3490,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -3521,7 +3514,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3533,13 +3526,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8720
 </t>
         </is>
       </c>
@@ -3569,8 +3562,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3581,25 +3573,24 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3624,138 +3615,139 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
-</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8826
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4382
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29526
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1469
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3774,139 +3766,137 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
-</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
+          <t xml:space="preserve">8724
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3925,142 +3915,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">3261
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>814</t>
+          <t xml:space="preserve">748
+</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4078,52 +4068,53 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">3261
+</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>363</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4135,13 +4126,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
@@ -4153,19 +4143,19 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -4176,8 +4166,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -4188,7 +4177,8 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -4199,8 +4189,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -4211,7 +4200,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4230,8 +4219,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4248,19 +4236,19 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -4272,7 +4260,8 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -4289,7 +4278,8 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -4300,19 +4290,19 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4330,25 +4320,24 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -4366,7 +4355,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">16
+54
 </t>
         </is>
       </c>
@@ -4385,17 +4375,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4406,24 +4398,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4435,31 +4428,30 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4477,48 +4469,47 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>081</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4542,14 +4533,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4566,58 +4555,58 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12396
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -4644,35 +4633,36 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4690,88 +4680,83 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -4798,13 +4783,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>855</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4821,13 +4806,13 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4846,13 +4831,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4870,31 +4854,31 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4905,54 +4889,52 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4976,13 +4958,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5001,19 +4983,19 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">4373
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5025,7 +5007,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5037,31 +5019,37 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -5072,13 +5060,13 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -5096,19 +5084,19 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -5119,19 +5107,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2
+78
 </t>
         </is>
       </c>
@@ -5150,13 +5138,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">32720
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -5168,12 +5156,14 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -5184,110 +5174,100 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5305,8 +5285,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5322,7 +5301,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5334,19 +5313,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5364,82 +5343,84 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">832
+</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">54
+5
 </t>
         </is>
       </c>
@@ -5458,144 +5439,136 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
-</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">31
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2216
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">6
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5613,144 +5586,139 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">3989
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2890
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">3266
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5769,36 +5737,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
+          <t xml:space="preserve">16835
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t xml:space="preserve">561
+</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5810,102 +5779,98 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">1035
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">4325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>836</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -5924,139 +5889,141 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
+          <t xml:space="preserve">3367
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">3600
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0029</t>
+          <t xml:space="preserve">2646
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>551</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13996
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">2526
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6075,91 +6042,85 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
-</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9251
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6171,49 +6132,46 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6231,142 +6189,144 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2024
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6384,142 +6344,143 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>0401</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">584
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6537,144 +6498,144 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488
+          <t xml:space="preserve">442
+2 6
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6692,126 +6653,120 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">3413
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1781
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>611</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6821,13 +6776,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6845,79 +6800,77 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6929,59 +6882,60 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">7335
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -6998,129 +6952,141 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1416
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">777
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18256
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t xml:space="preserve">2424
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">6 7
+57
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7139,23 +7105,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">2480
+</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7166,46 +7134,50 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>0564</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18256
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">20 8
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -7222,16 +7194,11 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">690
@@ -7246,26 +7213,27 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2424
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -728,36 +728,34 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">94375
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -769,7 +767,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -782,50 +780,49 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30226
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -836,8 +833,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -846,24 +842,9 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -877,51 +858,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -939,30 +910,26 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -974,46 +941,44 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t xml:space="preserve">741
+</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -1032,13 +997,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4316
-</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1056,43 +1020,38 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -1104,37 +1063,36 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">12329
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">16089
 </t>
         </is>
       </c>
@@ -1146,30 +1104,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1188,77 +1147,71 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">14373
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">2330
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
-</t>
-        </is>
-      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1673
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
@@ -1270,7 +1223,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1282,13 +1235,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">20221
 </t>
         </is>
       </c>
@@ -1300,30 +1253,31 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1276
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1342,22 +1296,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12972
+</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>526</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t xml:space="preserve">1262
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1368,13 +1326,14 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1385,66 +1344,66 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18656
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1462,19 +1421,20 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1492,39 +1452,30 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">16665
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1533,58 +1484,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">443
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">1943
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">1963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
+          <t xml:space="preserve">14409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1629
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">16173
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">13609
 </t>
         </is>
       </c>
@@ -1596,31 +1550,16 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1639,18 +1578,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t xml:space="preserve">3333
+</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3051
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1661,12 +1601,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1161
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1677,36 +1619,27 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5447
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1876
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -1718,40 +1651,42 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1264
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1763,13 +1698,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8065
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1788,30 +1723,31 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456
+          <t xml:space="preserve">14450
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1823,12 +1759,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1838,12 +1775,7 @@
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1852,26 +1784,25 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1882,7 +1813,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">19819
 </t>
         </is>
       </c>
@@ -1894,19 +1825,19 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -1918,16 +1849,11 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1955,18 +1881,20 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1977,7 +1905,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1989,14 +1917,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -2019,13 +1946,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
@@ -2043,41 +1970,42 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>533</t>
+          <t xml:space="preserve">53
+</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1247
+</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2096,12 +2024,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t xml:space="preserve">393567
+</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -2125,31 +2054,31 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
@@ -2167,18 +2096,14 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2190,7 +2115,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3247
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -2202,35 +2127,37 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1238
+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1977
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2249,19 +2176,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">139740
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1325
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2273,43 +2200,38 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2321,7 +2243,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
@@ -2339,13 +2261,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2375,13 +2297,14 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1930
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2411,28 +2334,31 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">1249
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -2444,19 +2370,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2465,15 +2390,10 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2497,13 +2417,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">1638
 </t>
         </is>
       </c>
@@ -2515,30 +2435,31 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">12411
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -2557,19 +2478,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">119928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2581,22 +2502,17 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2605,13 +2521,13 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
@@ -2623,48 +2539,49 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211222
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">11428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
+          <t xml:space="preserve">13687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5334415</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2673,26 +2590,17 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">14551
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2711,9 +2619,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-3986
-</t>
+          <t>399</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2730,7 +2636,8 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">12249
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2740,42 +2647,44 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2787,36 +2696,36 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1106
+</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -2828,19 +2737,19 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2859,7 +2768,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -2871,40 +2780,38 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1871
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2928,19 +2835,19 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2952,30 +2859,31 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>631</t>
+          <t xml:space="preserve">1631
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2256
 </t>
         </is>
       </c>
@@ -2987,14 +2895,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-8 179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3013,7 +2920,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4239
+          <t xml:space="preserve">14239
 </t>
         </is>
       </c>
@@ -3031,36 +2938,38 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">11248
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3071,25 +2980,24 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3113,8 +3021,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3125,7 +3032,8 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1258
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3136,21 +3044,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-44
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-818
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3169,42 +3075,43 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-1 8 4
-7
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3216,45 +3123,49 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">124080
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3266,12 +3177,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t xml:space="preserve">707
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3282,21 +3195,28 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">1205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3312,13 +3232,14 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">14335
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">1308
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3333,16 +3254,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3352,12 +3278,7 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3366,8 +3287,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3378,37 +3298,32 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n"/>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -3420,30 +3335,30 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
-8111
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3462,24 +3377,26 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">374 0
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3490,19 +3407,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3514,7 +3431,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3526,19 +3443,19 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3556,13 +3473,14 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">1564
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3573,24 +3491,25 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -3615,28 +3534,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t xml:space="preserve">19255
+</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t xml:space="preserve">1531
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">928
+</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>603</t>
+          <t xml:space="preserve">1603
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3653,101 +3576,83 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1355
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826
+          <t xml:space="preserve">18828
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382
+          <t xml:space="preserve">14372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29526
+          <t xml:space="preserve">12952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">11267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14110
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -3766,7 +3671,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t xml:space="preserve">3851
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3783,18 +3689,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -3819,31 +3726,26 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3861,19 +3763,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">1590
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
@@ -3885,19 +3787,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3915,31 +3817,31 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">13740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1257
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3956,16 +3858,11 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3974,13 +3871,13 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -3992,64 +3889,66 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">1313
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">9569
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">12242
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">17476
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4068,139 +3967,142 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1246
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4219,145 +4121,140 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">7208
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4375,140 +4272,145 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t xml:space="preserve">93893
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1398
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>081</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4527,59 +4429,61 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
+          <t xml:space="preserve">4085
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12396
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -4591,25 +4495,25 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -4621,47 +4525,49 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4680,139 +4586,145 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t xml:space="preserve">18564
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t xml:space="preserve">1503
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1919
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">14419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">11385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">11137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">13328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">18231
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">11243
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">13998
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4831,140 +4743,136 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>064</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t xml:space="preserve">1666
+</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4989,137 +4897,127 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">691
+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-78
+          <t xml:space="preserve">11188
 </t>
         </is>
       </c>
@@ -5138,136 +5036,137 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32720
+          <t xml:space="preserve">13970
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>816</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>495</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t xml:space="preserve">874
+</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1329
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">19477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1261
+</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5285,86 +5184,82 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">3624
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5373,13 +5268,13 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -5391,36 +5286,36 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0554</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-5
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5439,30 +5334,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t xml:space="preserve">1879
+</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -5471,22 +5368,28 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>241</t>
+          <t xml:space="preserve">2010
+</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5497,24 +5400,24 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">2093
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5526,7 +5429,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -5544,7 +5447,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5556,18 +5459,19 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5592,24 +5496,25 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5633,7 +5538,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5651,13 +5556,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -5669,19 +5574,19 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25938
 </t>
         </is>
       </c>
@@ -5699,26 +5604,31 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n"/>
+          <t xml:space="preserve">2050
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5737,28 +5647,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116835
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5767,7 +5662,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5785,7 +5680,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
@@ -5795,53 +5690,47 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4325
+          <t xml:space="preserve">14325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t xml:space="preserve">1657
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5850,27 +5739,17 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+      <c r="W37" s="3" t="n"/>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">3966
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">3424
 </t>
         </is>
       </c>
@@ -5895,20 +5774,19 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5919,28 +5797,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12111
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5949,30 +5821,31 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5984,46 +5857,49 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2526
-</t>
-        </is>
-      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6042,7 +5918,8 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t xml:space="preserve">14008
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6053,74 +5930,79 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1205
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
@@ -6132,13 +6014,13 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6149,29 +6031,32 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>768</t>
+          <t xml:space="preserve">1268
+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6189,19 +6074,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -6213,31 +6098,30 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -6255,25 +6139,25 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -6291,7 +6175,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
@@ -6309,24 +6193,26 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6344,7 +6230,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">14488
 </t>
         </is>
       </c>
@@ -6356,31 +6242,32 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6391,12 +6278,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0401</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -6408,7 +6296,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6432,7 +6320,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -6444,8 +6332,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6456,30 +6343,30 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6498,144 +6385,143 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-2 6
-</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">19249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>028</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6653,23 +6539,26 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">1320
+</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">1886
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6680,108 +6569,115 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27914
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1828
+</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
@@ -6806,19 +6702,19 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6835,7 +6731,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6847,98 +6743,82 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2286
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7335
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6952,45 +6832,26 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168711
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -7002,91 +6863,71 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18256
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">102342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16912
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">40844
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1848324382
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -7105,12 +6946,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">3117
+</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -7122,7 +6964,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -7134,7 +6976,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -7146,16 +6988,11 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7164,13 +7001,13 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18256
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 8
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -7188,20 +7025,25 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+          <t xml:space="preserve">2216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -7213,30 +7055,29 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">2242
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -728,34 +728,37 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94375
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">9124 11
 </t>
         </is>
       </c>
@@ -767,11 +770,16 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n"/>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 8
+</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -780,25 +788,25 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">11785
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -810,19 +818,20 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t xml:space="preserve">637
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -833,7 +842,8 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">277
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -858,10 +868,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -873,7 +887,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -885,20 +899,15 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -916,17 +925,22 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -941,19 +955,19 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -963,16 +977,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="3" t="n"/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">7261
 </t>
         </is>
       </c>
@@ -997,12 +1016,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t xml:space="preserve">8316
+</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1026,32 +1046,37 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n"/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1063,54 +1088,55 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12329
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16089
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -1122,13 +1148,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1147,54 +1173,62 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14373
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 82
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1205,13 +1239,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1223,7 +1257,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1235,13 +1269,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
@@ -1253,25 +1287,20 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779
+          <t xml:space="preserve">17729
 </t>
         </is>
       </c>
@@ -1296,7 +1325,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12972
+          <t xml:space="preserve">989716
 </t>
         </is>
       </c>
@@ -1308,13 +1337,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -1332,7 +1361,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1344,13 +1373,13 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1362,43 +1391,44 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t xml:space="preserve">954
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1421,7 +1451,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -1431,12 +1461,7 @@
 </t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1452,21 +1477,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">11526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1475,7 +1511,12 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2112
+</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1484,61 +1525,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14409
+          <t xml:space="preserve">18409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
+          <t xml:space="preserve">12173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">18319
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13609
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
@@ -1550,16 +1591,26 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">1261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="3" t="n"/>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114184
+</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -1578,19 +1629,20 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3051
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1607,13 +1659,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1623,10 +1675,15 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1636,10 +1693,15 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -1657,19 +1719,19 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
@@ -1681,7 +1743,8 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1692,13 +1755,13 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">8259
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
@@ -1723,7 +1786,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14450
+          <t xml:space="preserve">14451
 </t>
         </is>
       </c>
@@ -1741,7 +1804,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1759,23 +1822,28 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="n"/>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1784,76 +1852,81 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">2467
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">23 08
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1869,13 +1942,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3836
-</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1887,25 +1959,25 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1917,13 +1989,14 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1946,13 +2019,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1970,7 +2043,8 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1981,19 +2055,19 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -2005,7 +2079,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2024,13 +2098,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">393567
+          <t xml:space="preserve">0856
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -2054,7 +2128,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2066,19 +2140,19 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -2096,14 +2170,19 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2127,19 +2206,19 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2151,13 +2230,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2176,13 +2255,13 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139740
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325
+          <t xml:space="preserve">2325
 </t>
         </is>
       </c>
@@ -2206,17 +2285,22 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2225,13 +2309,13 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2243,14 +2327,13 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2267,7 +2350,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2328,7 +2411,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">16433
 </t>
         </is>
       </c>
@@ -2340,13 +2423,13 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2358,24 +2441,25 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2387,13 +2471,19 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2417,13 +2507,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
@@ -2435,13 +2525,13 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2453,7 +2543,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">17410
 </t>
         </is>
       </c>
@@ -2478,37 +2568,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119928
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">11299
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9918
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2527,43 +2617,42 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
-</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">10559
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
+          <t xml:space="preserve">44641
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
@@ -2575,13 +2664,14 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13687
+          <t xml:space="preserve">3687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334415</t>
+          <t xml:space="preserve">531
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2590,11 +2680,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1375
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14551
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
@@ -2619,12 +2719,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -2636,15 +2736,11 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12249
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2653,7 +2749,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2664,27 +2760,22 @@
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
+      <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2696,13 +2787,14 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t xml:space="preserve">1820
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2713,7 +2805,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2725,7 +2817,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">2482
 </t>
         </is>
       </c>
@@ -2768,44 +2860,43 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1871
-</t>
-        </is>
-      </c>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2817,37 +2908,36 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2859,13 +2949,13 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2883,13 +2973,13 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">4113
 </t>
         </is>
       </c>
@@ -2920,13 +3010,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14239
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">9225
 </t>
         </is>
       </c>
@@ -2938,19 +3027,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11248
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2962,13 +3051,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
@@ -2980,7 +3068,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -2992,36 +3080,38 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">875
+</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2618
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">12953
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">540
+</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3032,7 +3122,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">16558
 </t>
         </is>
       </c>
@@ -3044,22 +3134,17 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3075,13 +3160,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">8568
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
@@ -3093,7 +3178,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -3105,7 +3190,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3117,31 +3202,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124080
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3159,19 +3239,19 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3183,7 +3263,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">95 1
 </t>
         </is>
       </c>
@@ -3195,7 +3275,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3207,7 +3287,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
@@ -3232,13 +3312,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14335
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -3262,13 +3342,13 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3278,7 +3358,12 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3287,7 +3372,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3298,14 +3384,19 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -3323,7 +3414,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3335,13 +3426,14 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
@@ -3377,8 +3469,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 0
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3387,12 +3478,7 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+      <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3401,25 +3487,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3449,73 +3535,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1216
 </t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1564
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1216
-</t>
-        </is>
-      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3546,19 +3632,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">160274
 </t>
         </is>
       </c>
@@ -3576,48 +3662,58 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18828
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14372
+          <t xml:space="preserve">11372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
+          <t xml:space="preserve">15357
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11451
+</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3626,7 +3722,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12952
+          <t xml:space="preserve">2952
 </t>
         </is>
       </c>
@@ -3636,17 +3732,27 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107
+</t>
+        </is>
+      </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11267
+          <t xml:space="preserve">2267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">18110
 </t>
         </is>
       </c>
@@ -3671,13 +3777,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -3689,19 +3795,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -3713,11 +3819,16 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3726,26 +3837,31 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3763,19 +3879,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3787,19 +3903,15 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3817,36 +3929,37 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13740
+          <t xml:space="preserve">3740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3858,11 +3971,16 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81414 6
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3877,7 +3995,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -3889,30 +4007,31 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">1040
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9569
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
@@ -3924,13 +4043,13 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3942,13 +4061,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17476
+          <t xml:space="preserve">1748
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -3967,7 +4086,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -3979,8 +4098,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3997,13 +4115,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4015,7 +4133,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -4027,24 +4145,25 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4068,38 +4187,35 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="n"/>
       <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4121,7 +4237,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9522
 </t>
         </is>
       </c>
@@ -4133,13 +4249,13 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4155,10 +4271,15 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4170,7 +4291,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4182,31 +4303,31 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4218,31 +4339,30 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2098
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4254,7 +4374,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4272,7 +4393,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93893
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -4284,8 +4405,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4302,25 +4422,25 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4338,19 +4458,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">82813
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4362,7 +4482,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4374,26 +4494,25 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4404,7 +4523,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4429,7 +4548,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
@@ -4441,52 +4560,51 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8229
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
@@ -4495,7 +4613,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4507,13 +4625,13 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4525,7 +4643,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4543,7 +4661,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4555,13 +4673,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81828
 </t>
         </is>
       </c>
@@ -4586,37 +4704,37 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
+          <t xml:space="preserve">118364
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4634,13 +4752,13 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4652,55 +4770,55 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">91034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14419
+          <t xml:space="preserve">142419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13328
+          <t xml:space="preserve">3328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18231
+          <t xml:space="preserve">11231
 </t>
         </is>
       </c>
@@ -4712,14 +4830,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11243
-</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13998
-</t>
+          <t>394</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4743,12 +4859,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4760,18 +4876,20 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">105
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t xml:space="preserve">11824
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4786,10 +4904,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -4801,13 +4924,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>064</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4818,7 +4941,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4830,52 +4953,46 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
+          <t xml:space="preserve">666
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4891,49 +5008,55 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">9437
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4945,23 +5068,28 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">4215
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">310
@@ -4970,7 +5098,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4982,24 +5110,25 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">5606
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">2682
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11288
 </t>
         </is>
       </c>
@@ -5011,13 +5140,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11188
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5036,48 +5165,54 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13970
+          <t xml:space="preserve">3971
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
@@ -5089,12 +5224,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5112,42 +5248,43 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19477
+          <t xml:space="preserve">477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5159,7 +5296,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5184,13 +5321,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5208,19 +5345,19 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5232,7 +5369,8 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1024
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5255,11 +5393,16 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5268,31 +5411,32 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">78868
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>0554</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -5303,19 +5447,19 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">18328
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5340,55 +5484,55 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5400,24 +5544,25 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t xml:space="preserve">834
+</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5429,7 +5574,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -5441,25 +5586,25 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -5471,7 +5616,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5496,19 +5641,18 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">9243
 </t>
         </is>
       </c>
@@ -5532,13 +5676,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5556,13 +5700,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5574,25 +5718,25 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25938
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
@@ -5604,7 +5748,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050
+          <t xml:space="preserve">2958
 </t>
         </is>
       </c>
@@ -5616,22 +5760,17 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">8468
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5651,9 +5790,24 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14501
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1255
+</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5662,7 +5816,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">92241
 </t>
         </is>
       </c>
@@ -5680,7 +5834,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5690,11 +5844,21 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13965
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14325
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -5706,7 +5870,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5718,18 +5882,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t xml:space="preserve">3437
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
@@ -5739,8 +5904,18 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3966
@@ -5749,7 +5924,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -5786,7 +5961,8 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5797,22 +5973,28 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5821,25 +6003,25 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19 3
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5857,19 +6039,19 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
@@ -5881,7 +6063,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2 24 2
 </t>
         </is>
       </c>
@@ -5893,13 +6075,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5918,19 +6100,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">140018
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">4118
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -5942,7 +6124,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5952,27 +6134,22 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5984,7 +6161,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5996,19 +6173,19 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -6020,7 +6197,8 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t xml:space="preserve">5345
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6031,31 +6209,31 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">1754
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6080,13 +6258,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>94446</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -6098,30 +6275,31 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6139,7 +6317,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6151,13 +6329,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6175,7 +6353,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6187,31 +6365,31 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12172
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6230,14 +6408,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14488
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6260,31 +6437,31 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6320,7 +6497,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6332,7 +6509,8 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t xml:space="preserve">584
+</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6343,7 +6521,8 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6354,7 +6533,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6385,12 +6564,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -6402,13 +6582,13 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6420,30 +6600,31 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>028</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6455,7 +6636,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6479,19 +6660,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">2282
 </t>
         </is>
       </c>
@@ -6503,24 +6684,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1104
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">187080
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6539,19 +6721,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6569,19 +6751,19 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6617,19 +6799,19 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6641,32 +6823,26 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n"/>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27914
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6677,7 +6853,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6696,25 +6872,26 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6731,7 +6908,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
@@ -6755,17 +6932,20 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">2008
+</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6776,13 +6956,13 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6794,19 +6974,19 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">18223
 </t>
         </is>
       </c>
@@ -6834,88 +7014,123 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168711
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+          <t xml:space="preserve">188411
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8411
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1056
+</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">28161
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">121804
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101092106191
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102342
+          <t xml:space="preserve">02041
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
+          <t xml:space="preserve">168084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16912
+          <t xml:space="preserve">12572
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">12917
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">183179
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40844
+          <t xml:space="preserve">448414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11222
+</t>
+        </is>
+      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848324382
+          <t xml:space="preserve">9247
 </t>
         </is>
       </c>
@@ -6946,13 +7161,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">5117
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -6964,35 +7179,40 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11226
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7007,8 +7227,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7025,13 +7244,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -7043,7 +7262,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
@@ -7055,28 +7274,23 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">2188
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9247
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124 11
+          <t xml:space="preserve">91124 1
 </t>
         </is>
       </c>
@@ -776,13 +776,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8
+          <t xml:space="preserve">8 8 8
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
@@ -794,7 +794,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11785
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -887,7 +887,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -899,18 +899,13 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -925,7 +920,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -935,12 +930,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -967,7 +957,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -979,19 +969,19 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7261
+          <t xml:space="preserve">741
 </t>
         </is>
       </c>
@@ -1016,7 +1006,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316
+          <t xml:space="preserve">4326
 </t>
         </is>
       </c>
@@ -1046,25 +1036,25 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1118,13 +1108,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1173,19 +1163,19 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1197,19 +1187,19 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1227,25 +1217,25 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">2620
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -1300,7 +1290,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17729
+          <t xml:space="preserve">7279
 </t>
         </is>
       </c>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989716
+          <t xml:space="preserve">297 6
 </t>
         </is>
       </c>
@@ -1337,28 +1327,28 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1385,7 +1375,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1483,13 +1473,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11526
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1513,7 +1503,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409
+          <t xml:space="preserve">4409
 </t>
         </is>
       </c>
@@ -1567,13 +1557,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18319
+          <t xml:space="preserve">12319
 </t>
         </is>
       </c>
@@ -1601,16 +1591,21 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="3" t="n"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114184
+          <t xml:space="preserve">1141024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -1659,28 +1654,18 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1695,13 +1680,13 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">2193
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -1755,7 +1740,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1767,7 +1752,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1786,7 +1771,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14451
+          <t xml:space="preserve">24451
 </t>
         </is>
       </c>
@@ -1816,7 +1801,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1828,13 +1813,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1852,7 +1837,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2467
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -1864,7 +1849,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1876,7 +1861,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 08
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1888,13 +1873,13 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">587
 </t>
         </is>
       </c>
@@ -1906,7 +1891,8 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">247 16
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1923,7 +1909,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1942,12 +1928,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1971,7 +1957,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1989,7 +1975,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2073,13 +2059,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2098,7 +2084,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2116,7 +2102,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2355
 </t>
         </is>
       </c>
@@ -2140,13 +2126,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2224,13 +2210,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -2261,7 +2247,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2285,7 +2271,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2295,12 +2281,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2315,7 +2296,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2333,7 +2314,8 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2350,7 +2332,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2380,13 +2362,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2411,7 +2393,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16433
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
@@ -2423,7 +2405,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2435,19 +2417,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2459,7 +2441,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">16 8
 </t>
         </is>
       </c>
@@ -2519,7 +2501,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -2543,7 +2525,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17410
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2574,19 +2556,19 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11299
+          <t xml:space="preserve">192499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9918
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2602,7 +2584,12 @@
 </t>
         </is>
       </c>
-      <c r="I16" s="3" t="n"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2617,30 +2604,30 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
+          <t xml:space="preserve">9246
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10559
+          <t xml:space="preserve">1058
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44641
+          <t xml:space="preserve">4448
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2652,7 +2639,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2719,12 +2706,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">398
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2740,7 +2728,12 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2749,18 +2742,21 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -2775,7 +2771,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2793,7 +2789,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">282240
 </t>
         </is>
       </c>
@@ -2805,25 +2801,25 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2482
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2835,13 +2831,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2860,7 +2856,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2872,43 +2868,47 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1713
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2925,13 +2925,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2967,19 +2967,19 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2506
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4113
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9225
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3051,7 +3051,8 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -3092,19 +3093,19 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2618
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12953
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3122,7 +3123,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16558
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -3140,7 +3141,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -3160,13 +3161,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568
+          <t xml:space="preserve">9568
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3178,7 +3179,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3200,13 +3201,12 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3227,19 +3227,19 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3251,13 +3251,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
@@ -3275,8 +3275,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3420,7 +3419,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2089
 </t>
         </is>
       </c>
@@ -3444,7 +3443,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">8508
 </t>
         </is>
       </c>
@@ -3469,7 +3468,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>344</t>
+          <t xml:space="preserve">3741
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3478,7 +3478,11 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3487,7 +3491,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
@@ -3499,7 +3503,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3577,19 +3581,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1935
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3601,7 +3605,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3626,13 +3630,13 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3644,7 +3648,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160274
+          <t xml:space="preserve">6059
 </t>
         </is>
       </c>
@@ -3668,7 +3672,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">4953
 </t>
         </is>
       </c>
@@ -3692,25 +3696,25 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11372
+          <t xml:space="preserve">4372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15357
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11451
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
@@ -3734,13 +3738,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3752,7 +3756,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -3777,25 +3781,25 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -3807,7 +3811,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3819,7 +3823,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3843,7 +3847,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3855,13 +3859,13 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3873,7 +3877,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23 8
 </t>
         </is>
       </c>
@@ -3935,19 +3939,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -3959,40 +3963,40 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 6
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81414 6
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4001,25 +4005,25 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">31 5
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4031,19 +4035,19 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4067,7 +4071,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4127,7 +4131,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -4151,7 +4155,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">89 2
 </t>
         </is>
       </c>
@@ -4181,7 +4185,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4193,7 +4197,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4237,25 +4241,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522
+          <t xml:space="preserve">3548
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4267,13 +4270,13 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4309,7 +4312,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -4327,7 +4330,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4345,18 +4348,18 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>634</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4368,7 +4371,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4405,7 +4408,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4416,19 +4420,19 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4458,7 +4462,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82813
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4470,7 +4474,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4500,7 +4504,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4512,18 +4516,18 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4548,30 +4552,29 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8229
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4613,7 +4616,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4625,7 +4628,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4643,13 +4646,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">2245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4673,19 +4676,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81828
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4704,7 +4707,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118364
+          <t xml:space="preserve">118564
 </t>
         </is>
       </c>
@@ -4716,13 +4719,13 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -4740,7 +4743,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4758,7 +4761,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">9296
 </t>
         </is>
       </c>
@@ -4770,25 +4773,25 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91034
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142419
+          <t xml:space="preserve">4419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">2385
 </t>
         </is>
       </c>
@@ -4812,13 +4815,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4830,12 +4833,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>613</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>439</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4859,19 +4862,18 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>096</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4888,7 +4890,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4904,15 +4906,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4930,12 +4927,13 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4953,7 +4951,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4964,13 +4963,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">28246
 </t>
         </is>
       </c>
@@ -4982,13 +4981,13 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5008,13 +5007,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">4128
 </t>
         </is>
       </c>
@@ -5026,7 +5025,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -5044,7 +5043,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5056,85 +5055,85 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4215
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5606
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -5146,7 +5145,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -5165,13 +5164,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3971
-</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5183,7 +5181,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5195,14 +5193,13 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5212,7 +5209,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5254,7 +5251,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2389
 </t>
         </is>
       </c>
@@ -5296,13 +5293,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">17276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5327,7 +5324,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -5345,7 +5342,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5369,7 +5366,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5411,7 +5408,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5423,19 +5420,19 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78868
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5447,13 +5444,13 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18328
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5478,7 +5475,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5544,13 +5541,13 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5586,19 +5583,19 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5610,13 +5607,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5647,24 +5644,24 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19 0 1
 </t>
         </is>
       </c>
@@ -5682,7 +5679,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -5700,7 +5697,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5736,7 +5733,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -5748,19 +5745,19 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2958
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8468
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5792,19 +5789,19 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14501
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5816,7 +5813,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92241
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5846,13 +5843,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5870,7 +5867,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1396
 </t>
         </is>
       </c>
@@ -5882,7 +5879,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">12560
 </t>
         </is>
       </c>
@@ -5973,7 +5970,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5985,13 +5982,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6039,7 +6035,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6051,7 +6047,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -6063,7 +6059,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 24 2
+          <t xml:space="preserve">224 1
 </t>
         </is>
       </c>
@@ -6075,7 +6071,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
@@ -6100,13 +6096,13 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140018
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4118
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -6124,20 +6120,20 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1585
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6149,7 +6145,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6161,7 +6157,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2884
 </t>
         </is>
       </c>
@@ -6173,31 +6169,31 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5345
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6221,19 +6217,19 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6258,7 +6254,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6275,109 +6271,109 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1890
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2083
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12172
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -6389,7 +6385,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -6408,13 +6404,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6425,7 +6421,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6437,25 +6433,25 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6533,13 +6529,13 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -6564,13 +6560,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">14645
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6660,22 +6656,22 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2282
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282
-</t>
-        </is>
-      </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">275
@@ -6690,13 +6686,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187080
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -6721,7 +6717,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -6763,7 +6759,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6799,7 +6795,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -6827,7 +6823,12 @@
 </t>
         </is>
       </c>
-      <c r="U43" s="3" t="n"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
@@ -6842,7 +6843,7 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>531</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6872,7 +6873,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -6908,13 +6909,13 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6932,26 +6933,24 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -6962,7 +6961,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6974,28 +6973,23 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
@@ -7014,43 +7008,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188411
+          <t xml:space="preserve">1682111
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
+          <t xml:space="preserve">8251
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1833
 </t>
         </is>
       </c>
@@ -7062,87 +7055,92 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28161
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121804
+          <t xml:space="preserve">19104
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101092106191
+          <t xml:space="preserve">100921059
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02041
+          <t xml:space="preserve">0342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168084
+          <t xml:space="preserve">1404
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12572
+          <t xml:space="preserve">2575
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12917
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183179
+          <t xml:space="preserve">13820
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448414
+          <t xml:space="preserve">4840
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">815
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11222
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9247
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7161,7 +7159,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
+          <t xml:space="preserve">3117
 </t>
         </is>
       </c>
@@ -7185,7 +7183,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -7197,7 +7195,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11226
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7209,7 +7207,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -7227,7 +7225,8 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>605</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7244,7 +7243,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -7280,13 +7279,13 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91124 1
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -776,19 +776,19 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8 8
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
@@ -842,13 +842,13 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -870,7 +870,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>621</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -899,13 +899,23 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -930,7 +940,12 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -945,7 +960,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -957,7 +972,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1006,8 +1021,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4326
-</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1024,7 +1038,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -1042,19 +1056,19 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -1114,7 +1128,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1173,12 +1187,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
@@ -1193,13 +1202,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1211,31 +1220,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
@@ -1247,7 +1256,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1265,7 +1274,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
@@ -1281,22 +1290,27 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="3" t="n"/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7279
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1315,20 +1329,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297 6
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1339,7 +1352,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -1375,7 +1388,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1423,7 +1436,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1441,17 +1454,22 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1752
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1473,25 +1491,25 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">8526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1503,7 +1521,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1515,7 +1533,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -1557,13 +1575,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">16173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12319
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -1593,19 +1611,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141024
+          <t xml:space="preserve">4024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1654,18 +1672,28 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1680,7 +1708,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1704,7 +1732,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -1771,7 +1799,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24451
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1789,19 +1817,19 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1813,13 +1841,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1837,68 +1865,66 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25 8
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">587
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247 16
-</t>
-        </is>
-      </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1928,12 +1954,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t xml:space="preserve">383
+</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1957,7 +1984,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1975,7 +2002,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2005,7 +2032,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2053,13 +2080,13 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">11977
 </t>
         </is>
       </c>
@@ -2084,7 +2111,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -2102,7 +2129,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2222,7 +2249,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2241,7 +2268,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -2271,7 +2298,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2281,7 +2308,12 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2296,7 +2328,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2314,7 +2346,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2344,7 +2376,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -2362,14 +2394,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2393,7 +2424,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
+          <t xml:space="preserve">1433
 </t>
         </is>
       </c>
@@ -2405,7 +2436,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
@@ -2423,7 +2454,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2441,7 +2472,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2453,7 +2484,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -2501,13 +2532,13 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -2519,7 +2550,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -2531,7 +2562,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2550,13 +2581,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">19928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192499
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
@@ -2574,54 +2605,48 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9246
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1058
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4448
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
@@ -2639,13 +2664,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">10425
 </t>
         </is>
       </c>
@@ -2675,8 +2700,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2706,7 +2730,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">3998
 </t>
         </is>
       </c>
@@ -2730,31 +2754,38 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115515
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -2771,7 +2802,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2789,19 +2820,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282240
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -2819,7 +2850,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2856,13 +2887,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -2874,7 +2904,8 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2885,19 +2916,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2908,30 +2939,31 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -2955,7 +2987,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -2973,13 +3005,13 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3010,7 +3042,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t xml:space="preserve">22234
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3051,13 +3084,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -3069,7 +3102,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3093,7 +3126,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -3145,7 +3178,11 @@
 </t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3161,8 +3198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9568
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3185,7 +3221,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -3201,10 +3237,16 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -3227,7 +3269,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3239,13 +3281,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">12415
 </t>
         </is>
       </c>
@@ -3257,13 +3299,13 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">707
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 1
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3275,7 +3317,8 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3365,22 +3408,22 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">867
@@ -3389,7 +3432,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3413,13 +3456,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3443,7 +3486,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8508
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -3468,37 +3511,37 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741
+          <t xml:space="preserve">23746
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2318
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">12475
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -3527,7 +3570,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
@@ -3569,7 +3612,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">2564
 </t>
         </is>
       </c>
@@ -3581,7 +3624,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -3624,13 +3667,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
+          <t xml:space="preserve">1925
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
@@ -3648,7 +3691,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6059
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -3666,13 +3709,13 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4953
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -3708,61 +3751,60 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2952
+          <t xml:space="preserve">28952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3781,7 +3823,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">13985
 </t>
         </is>
       </c>
@@ -3793,25 +3835,25 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -3847,7 +3889,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3865,7 +3907,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3877,7 +3919,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 8
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3889,7 +3931,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3911,7 +3953,12 @@
 </t>
         </is>
       </c>
-      <c r="Y24" s="3" t="n"/>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">54
@@ -3933,25 +3980,25 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">23740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
@@ -3969,8 +4016,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3981,7 +4027,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4005,31 +4051,31 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 5
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4041,7 +4087,7 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -4059,7 +4105,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -4071,7 +4117,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -4090,7 +4136,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
@@ -4102,7 +4148,8 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4119,7 +4166,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -4131,7 +4178,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4155,7 +4202,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89 2
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4185,28 +4232,28 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -4215,11 +4262,16 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="n"/>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4241,13 +4293,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3548
+          <t xml:space="preserve">13544
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4270,13 +4322,13 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4312,7 +4364,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -4348,13 +4400,14 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -4371,8 +4424,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4396,7 +4448,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3893
 </t>
         </is>
       </c>
@@ -4444,7 +4496,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4504,19 +4556,20 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4533,8 +4586,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4558,12 +4610,14 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4574,7 +4628,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4586,7 +4640,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4598,7 +4652,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4616,7 +4670,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4628,7 +4682,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4646,13 +4700,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -4664,7 +4718,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -4707,20 +4761,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118564
+          <t xml:space="preserve">18564
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4731,13 +4784,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
@@ -4761,7 +4814,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9296
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4773,7 +4826,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
@@ -4791,7 +4844,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -4815,7 +4868,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4833,12 +4886,14 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>439</t>
+          <t xml:space="preserve">3998
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4862,23 +4917,25 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">371
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>096</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4896,17 +4953,22 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4951,13 +5013,13 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -4969,7 +5031,7 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -4981,17 +5043,22 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5007,13 +5074,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4128
+          <t xml:space="preserve">13528
 </t>
         </is>
       </c>
@@ -5025,13 +5092,13 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1669
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
@@ -5043,7 +5110,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5055,7 +5122,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5073,7 +5140,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -5085,8 +5152,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5115,19 +5181,19 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
@@ -5139,13 +5205,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5164,12 +5230,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t xml:space="preserve">3979
+</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
@@ -5204,12 +5271,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5251,7 +5319,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5263,43 +5331,43 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17276
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5318,7 +5386,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
+          <t xml:space="preserve">13624
 </t>
         </is>
       </c>
@@ -5348,7 +5416,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5360,13 +5428,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5432,7 +5500,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -5450,7 +5518,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -5505,7 +5573,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5529,7 +5597,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5541,7 +5609,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5583,13 +5651,13 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5638,13 +5706,14 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5661,7 +5730,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0 1
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5673,13 +5742,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5697,7 +5766,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5745,7 +5814,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5757,7 +5826,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5767,7 +5836,11 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5783,7 +5856,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116835
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
@@ -5795,19 +5868,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
@@ -5831,7 +5904,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
@@ -5849,7 +5922,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
@@ -5879,7 +5952,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12560
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -5940,7 +6013,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
+          <t xml:space="preserve">23267
 </t>
         </is>
       </c>
@@ -5958,7 +6031,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
@@ -5982,7 +6055,8 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -5999,13 +6073,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 3
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -6035,7 +6109,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6047,7 +6121,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -6059,7 +6133,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 1
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6077,7 +6151,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6096,7 +6170,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">14008
 </t>
         </is>
       </c>
@@ -6120,17 +6194,22 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">139
@@ -6157,7 +6236,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6169,13 +6248,13 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6187,7 +6266,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6211,7 +6290,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -6254,30 +6333,31 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">2841
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
@@ -6313,7 +6393,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -6361,13 +6441,13 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2083
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6379,13 +6459,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
@@ -6404,24 +6484,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
+          <t xml:space="preserve">2448
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -6439,7 +6520,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6529,7 +6610,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6541,7 +6622,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6560,7 +6641,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14645
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -6584,7 +6665,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6614,7 +6695,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6638,7 +6719,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6656,13 +6737,13 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1500
 </t>
         </is>
       </c>
@@ -6680,25 +6761,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -6717,7 +6798,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
@@ -6729,7 +6810,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -6741,7 +6822,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6783,19 +6864,19 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6813,7 +6894,7 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -6825,7 +6906,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6843,12 +6924,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -6891,7 +6972,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -6915,7 +6996,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6927,30 +7008,31 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2041
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -6973,23 +7055,28 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n"/>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
@@ -7008,42 +7095,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682111
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8251
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t xml:space="preserve">1056
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -7055,27 +7142,31 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19104
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1092
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100921059
+          <t xml:space="preserve">12181
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0342
-</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -7086,55 +7177,50 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13820
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">483904
 </t>
         </is>
       </c>
@@ -7171,7 +7257,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7183,13 +7269,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">11676
 </t>
         </is>
       </c>
@@ -7205,12 +7291,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7231,7 +7312,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -7243,7 +7324,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -7279,13 +7360,13 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -728,128 +728,107 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X4" s="3" t="n"/>
@@ -875,135 +854,113 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1026,140 +983,117 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1177,141 +1111,118 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1329,14 +1240,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1346,128 +1255,107 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1485,146 +1373,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1642,146 +1506,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1799,104 +1639,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1906,20 +1729,17 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1929,14 +1749,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1954,146 +1772,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
+          <t>383</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2111,146 +1905,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2268,134 +2038,112 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2405,8 +2153,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2424,146 +2171,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2581,26 +2304,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2610,20 +2329,17 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2634,68 +2350,57 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2705,14 +2410,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2730,146 +2433,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115515
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2892,38 +2571,32 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2933,98 +2606,82 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3042,140 +2699,117 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3203,140 +2837,117 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12415
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3354,146 +2965,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3511,32 +3098,27 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12475
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3546,110 +3128,92 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3667,110 +3231,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3780,32 +3326,27 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3823,146 +3364,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3980,38 +3497,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4021,104 +3532,87 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4136,146 +3630,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4293,8 +3763,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4304,122 +3773,102 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4429,8 +3878,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4448,140 +3896,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4604,146 +4029,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4761,14 +4162,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4778,128 +4177,107 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4917,146 +4295,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5074,80 +4428,67 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13528
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5157,62 +4498,52 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5230,38 +4561,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5271,104 +4596,87 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5386,146 +4694,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5543,146 +4827,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5700,140 +4960,117 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5856,146 +5093,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6013,146 +5226,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6170,146 +5359,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6327,146 +5492,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6484,146 +5625,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6641,146 +5758,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6798,128 +5891,107 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6929,14 +6001,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6954,74 +6024,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2041
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -7031,50 +6089,42 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X44" s="3" t="n"/>
@@ -7100,68 +6150,57 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -7171,63 +6210,53 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7245,129 +6274,112 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n"/>

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3389,34 +3389,34 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>193</t>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5625,17 +5625,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/209/original_transcribed_data.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>649</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6284,49 +6284,49 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>202</t>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
